--- a/tests/sample_data/CatchByYMGOLoLa.xlsx
+++ b/tests/sample_data/CatchByYMGOLoLa.xlsx
@@ -352,7 +352,7 @@
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:A4"/>
+  <dimension ref="A1:G21"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -361,18 +361,774 @@
           <t>Catch of southern bluefin tuna by year, month, gear, ocean and 5 degree grid</t>
         </is>
       </c>
+      <c r="B1" s="1" t="inlineStr">
+        <is>
+          <t>...2</t>
+        </is>
+      </c>
+      <c r="C1" s="1" t="inlineStr">
+        <is>
+          <t>...3</t>
+        </is>
+      </c>
+      <c r="D1" s="1" t="inlineStr">
+        <is>
+          <t>...4</t>
+        </is>
+      </c>
+      <c r="E1" s="1" t="inlineStr">
+        <is>
+          <t>...5</t>
+        </is>
+      </c>
+      <c r="F1" s="1" t="inlineStr">
+        <is>
+          <t>...6</t>
+        </is>
+      </c>
+      <c r="G1" s="1" t="inlineStr">
+        <is>
+          <t>...7</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>Catches are presented as whole weights in tonnes.  All figures, particularly for the last reported year of catch are subject to change as improved data or estimates become available.</t>
+          <t>1972</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C2" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="D2" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="E2" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="F2" t="inlineStr">
+        <is>
+          <t>-45</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>9.9681869455541001</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>1973</t>
+        </is>
+      </c>
+      <c r="B3" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C3" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="D3" t="inlineStr">
+        <is>
+          <t>Atlantic</t>
+        </is>
+      </c>
+      <c r="E3" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="F3" t="inlineStr">
+        <is>
+          <t>-40</t>
+        </is>
+      </c>
+      <c r="G3" t="inlineStr">
+        <is>
+          <t>20.352055642232202</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Note:  reviews of SBT data in 2006 indicated that southern bluefin tuna catches may have been substantially under-reported over the previous 10-20 years and the data presented here do not yet include estimates for this unreported catch.</t>
+          <t>1973</t>
+        </is>
+      </c>
+      <c r="B4" t="inlineStr">
+        <is>
+          <t>9</t>
+        </is>
+      </c>
+      <c r="C4" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="D4" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="E4" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>-45</t>
+        </is>
+      </c>
+      <c r="G4" t="inlineStr">
+        <is>
+          <t>13.456300318746401</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>1974</t>
+        </is>
+      </c>
+      <c r="B5" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C5" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="D5" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="E5" t="inlineStr">
+        <is>
+          <t>140</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr">
+        <is>
+          <t>-45</t>
+        </is>
+      </c>
+      <c r="G5" t="inlineStr">
+        <is>
+          <t>4.9937886965731098</t>
+        </is>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>1976</t>
+        </is>
+      </c>
+      <c r="B6" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C6" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="D6" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="E6" t="inlineStr">
+        <is>
+          <t>90</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>-40</t>
+        </is>
+      </c>
+      <c r="G6" t="inlineStr">
+        <is>
+          <t>9.6733755042070495</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>1977</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C7" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="D7" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="E7" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>-35</t>
+        </is>
+      </c>
+      <c r="G7" t="inlineStr">
+        <is>
+          <t>390.02115076880199</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>1977</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="C8" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+      <c r="D8" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="E8" t="inlineStr">
+        <is>
+          <t>145</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr">
+        <is>
+          <t>-35</t>
+        </is>
+      </c>
+      <c r="G8" t="inlineStr">
+        <is>
+          <t>348.04578028247403</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>1979</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C9" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="D9" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="E9" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="F9" t="inlineStr">
+        <is>
+          <t>-45</t>
+        </is>
+      </c>
+      <c r="G9" t="inlineStr">
+        <is>
+          <t>15.1968195439635</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>1980</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C10" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="D10" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="E10" t="inlineStr">
+        <is>
+          <t>30</t>
+        </is>
+      </c>
+      <c r="F10" t="inlineStr">
+        <is>
+          <t>-40</t>
+        </is>
+      </c>
+      <c r="G10" t="inlineStr">
+        <is>
+          <t>811.61031924082101</t>
+        </is>
+      </c>
+    </row>
+    <row r="11">
+      <c r="A11" t="inlineStr">
+        <is>
+          <t>1982</t>
+        </is>
+      </c>
+      <c r="B11" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C11" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="D11" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="E11" t="inlineStr">
+        <is>
+          <t>75</t>
+        </is>
+      </c>
+      <c r="F11" t="inlineStr">
+        <is>
+          <t>-30</t>
+        </is>
+      </c>
+      <c r="G11" t="inlineStr">
+        <is>
+          <t>1.0089999999999999</t>
+        </is>
+      </c>
+    </row>
+    <row r="12">
+      <c r="A12" t="inlineStr">
+        <is>
+          <t>1992</t>
+        </is>
+      </c>
+      <c r="B12" t="inlineStr">
+        <is>
+          <t>5</t>
+        </is>
+      </c>
+      <c r="C12" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="D12" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="E12" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr">
+        <is>
+          <t>-35</t>
+        </is>
+      </c>
+      <c r="G12" t="inlineStr">
+        <is>
+          <t>2.7528827370347302</t>
+        </is>
+      </c>
+    </row>
+    <row r="13">
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>1993</t>
+        </is>
+      </c>
+      <c r="B13" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
+      <c r="C13" t="inlineStr">
+        <is>
+          <t>BB</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>135</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>-35</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>22.519971644233198</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>1994</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>130</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>-45</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>24.6054216320411</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>1998</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>150</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>-35</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>73.112157063796602</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>2008</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>95</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>-30</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>8.1988415999999995E-2</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>2009</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>-30</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>1.046331782</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>2014</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>6</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>Atlantic</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>-50</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>-35</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0.13897305900000001</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>2015</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>7</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>Indian</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>100</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>-30</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>46.896699092842198</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>2023</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>3</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>Atlantic</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>-40</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>32.480509336377203</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>2024</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>LL</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>Pacific</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>175</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>-30</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>6.1965253999999996</t>
         </is>
       </c>
     </row>
@@ -383,7 +1139,7 @@
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:B6"/>
+  <dimension ref="A1:B10"/>
   <sheetFormatPr defaultRowHeight="15"/>
   <sheetData>
     <row r="1" s="1" customFormat="1">
@@ -398,51 +1154,111 @@
         </is>
       </c>
     </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Code</t>
+        </is>
+      </c>
+      <c r="B2" t="inlineStr">
+        <is>
+          <t>Description</t>
+        </is>
+      </c>
+    </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Code</t>
+          <t>BB</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>Description</t>
+          <t>Baitboat (Pole and Line)</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>BB</t>
+          <t>GILL</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>Baitboat (Pole and Line)</t>
+          <t>Gillnet</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>GILL</t>
+          <t>HAND</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>Gillnet</t>
+          <t>Handline</t>
         </is>
       </c>
     </row>
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>HAND</t>
+          <t>LL</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>Handline</t>
+          <t>Longline</t>
+        </is>
+      </c>
+    </row>
+    <row r="7">
+      <c r="A7" t="inlineStr">
+        <is>
+          <t>PS</t>
+        </is>
+      </c>
+      <c r="B7" t="inlineStr">
+        <is>
+          <t>Purse Seine</t>
+        </is>
+      </c>
+    </row>
+    <row r="8">
+      <c r="A8" t="inlineStr">
+        <is>
+          <t>SURF</t>
+        </is>
+      </c>
+      <c r="B8" t="inlineStr">
+        <is>
+          <t>Surface fisheries unclassified</t>
+        </is>
+      </c>
+    </row>
+    <row r="9">
+      <c r="A9" t="inlineStr">
+        <is>
+          <t>TROL</t>
+        </is>
+      </c>
+      <c r="B9" t="inlineStr">
+        <is>
+          <t>Troll</t>
+        </is>
+      </c>
+    </row>
+    <row r="10">
+      <c r="A10" t="inlineStr">
+        <is>
+          <t>UNCL</t>
+        </is>
+      </c>
+      <c r="B10" t="inlineStr">
+        <is>
+          <t>Unclassified</t>
         </is>
       </c>
     </row>
